--- a/artfynd/A 30248-2025 artfynd.xlsx
+++ b/artfynd/A 30248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126353231</v>
       </c>
       <c r="B2" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>126383839</v>
       </c>
       <c r="B3" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>126353232</v>
       </c>
       <c r="B4" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126354321</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
